--- a/test/fixtures/sample.xlsx
+++ b/test/fixtures/sample.xlsx
@@ -463,7 +463,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kiln fixture marker 4711</v>
+        <v>Recast fixture marker 4711</v>
       </c>
     </row>
   </sheetData>
